--- a/AAII_Financials/Yearly/UHT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UHT_YR_FIN.xlsx
@@ -4090,7 +4090,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>27100</v>
+        <v>26200</v>
       </c>
       <c r="E83" s="3">
         <v>25600</v>
